--- a/Excel/MapGroupConfig.xlsx
+++ b/Excel/MapGroupConfig.xlsx
@@ -26,8 +26,62 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>admin</author>
+  </authors>
+  <commentList>
+    <comment ref="G3" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>admin:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+组合掉落</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="K3" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>admin:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+组合掉落</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="63">
   <si>
     <t>_Id</t>
   </si>
@@ -41,85 +95,181 @@
     <t>Memo</t>
   </si>
   <si>
+    <t>地图Id掉落</t>
+  </si>
+  <si>
+    <t>DropRateList</t>
+  </si>
+  <si>
+    <t>BaseIdList</t>
+  </si>
+  <si>
+    <t>BaseRateList</t>
+  </si>
+  <si>
     <t>Id</t>
   </si>
   <si>
+    <t>DropIdList</t>
+  </si>
+  <si>
     <t>int</t>
   </si>
   <si>
     <t>string</t>
   </si>
   <si>
+    <t>int[]</t>
+  </si>
+  <si>
     <t>落日平原</t>
   </si>
   <si>
     <t>（Lv1-5）—— 荒芜草原，小野兽与游荡亡灵</t>
   </si>
   <si>
+    <t>2006,4002,5001</t>
+  </si>
+  <si>
+    <t>1,1,1</t>
+  </si>
+  <si>
+    <t>30001,180006,20005,20006</t>
+  </si>
+  <si>
+    <t>1,1,2,2</t>
+  </si>
+  <si>
     <t>幽暗沼泽</t>
   </si>
   <si>
     <t>（Lv6-10）—— 毒雾弥漫，虫蚁与腐生怪</t>
   </si>
   <si>
+    <t>2012,4004,5002</t>
+  </si>
+  <si>
+    <t>30001,180012,20011,20012</t>
+  </si>
+  <si>
     <t>碎石矿场</t>
   </si>
   <si>
     <t>（Lv11-15）—— 废弃矿洞，傀儡与矿工变种</t>
   </si>
   <si>
+    <t>2018,4006,5003</t>
+  </si>
+  <si>
+    <t>30001,180018,20017,20018</t>
+  </si>
+  <si>
     <t>枯骨荒漠</t>
   </si>
   <si>
     <t>（Lv16-20）—— 干旱沙海，亡灵与骸骨</t>
   </si>
   <si>
+    <t>2024,4007,5004</t>
+  </si>
+  <si>
+    <t>30001,180024,20023,20024</t>
+  </si>
+  <si>
+    <t>#</t>
+  </si>
+  <si>
     <t>迷雾森林</t>
   </si>
   <si>
     <t>（Lv21-25）—— 幻术迷林，精灵与野兽</t>
   </si>
   <si>
+    <t>2005,4002,5001</t>
+  </si>
+  <si>
+    <t>30001,180005</t>
+  </si>
+  <si>
+    <t>1,1</t>
+  </si>
+  <si>
     <t>熔火地穴</t>
   </si>
   <si>
     <t>（Lv26-30）—— 岩浆河流，火焰恶魔</t>
   </si>
   <si>
+    <t>30001,180006</t>
+  </si>
+  <si>
     <t>雷光废墟</t>
   </si>
   <si>
     <t>（Lv31-35）—— 古代魔法遗迹，雷电元素</t>
   </si>
   <si>
+    <t>2007,4003,5002</t>
+  </si>
+  <si>
+    <t>30001,180007</t>
+  </si>
+  <si>
     <t>冰封王陵</t>
   </si>
   <si>
     <t>（Lv36-40）—— 永冻墓场，冰霜亡灵</t>
   </si>
   <si>
+    <t>2008,4003,5002</t>
+  </si>
+  <si>
+    <t>30001,180008</t>
+  </si>
+  <si>
     <t>诅咒祭坛</t>
   </si>
   <si>
     <t>（Lv41-45）—— 邪教圣地，高阶恶魔</t>
   </si>
   <si>
+    <t>2009,4003,5002</t>
+  </si>
+  <si>
+    <t>30001,180009</t>
+  </si>
+  <si>
     <t>虚空裂谷</t>
   </si>
   <si>
     <t>（Lv46-50）—— 空间扭曲，异界生物</t>
   </si>
   <si>
+    <t>2010,4004,5002</t>
+  </si>
+  <si>
+    <t>30001,180010</t>
+  </si>
+  <si>
     <t>龙眠之地</t>
   </si>
   <si>
     <t>（Lv51-55）—— 远古龙巢，龙族与亚龙</t>
   </si>
   <si>
+    <t>2011,4004,5002</t>
+  </si>
+  <si>
+    <t>30001,180011</t>
+  </si>
+  <si>
     <t>永恒神界</t>
   </si>
   <si>
     <t>（Lv56-60）—— 失落神域，法则化身</t>
+  </si>
+  <si>
+    <t>30001,180012</t>
   </si>
 </sst>
 </file>
@@ -132,7 +282,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -296,6 +446,17 @@
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="34">
@@ -752,10 +913,13 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1113,18 +1277,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:F17"/>
-  <sheetFormatPr defaultColWidth="9.25454545454545" defaultRowHeight="18" customHeight="1" outlineLevelCol="5"/>
+  <dimension ref="A3:N17"/>
+  <sheetFormatPr defaultColWidth="9.25454545454545" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9.25454545454545" style="1" customWidth="1"/>
     <col min="4" max="4" width="16.6363636363636" style="1" customWidth="1"/>
     <col min="5" max="5" width="16.1818181818182" style="1" customWidth="1"/>
     <col min="6" max="6" width="40.4545454545455" style="1" customWidth="1"/>
-    <col min="7" max="16377" width="9.25454545454545" style="1" customWidth="1"/>
+    <col min="7" max="14" width="24.2727272727273" style="1" customWidth="1"/>
+    <col min="15" max="16377" width="9.25454545454545" style="1" customWidth="1"/>
     <col min="16378" max="16384" width="9.25454545454545" style="1"/>
   </cols>
   <sheetData>
-    <row r="3" customHeight="1" spans="3:6">
+    <row r="3" customHeight="1" spans="1:14">
       <c r="C3" s="2" t="s">
         <v>0</v>
       </c>
@@ -1137,10 +1302,26 @@
       <c r="F3" s="2" t="s">
         <v>3</v>
       </c>
+      <c r="G3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2"/>
+      <c r="M3" s="2"/>
+      <c r="N3" s="2"/>
     </row>
-    <row r="4" customHeight="1" spans="3:6">
+    <row r="4" customHeight="1" spans="1:14">
       <c r="C4" s="2" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>1</v>
@@ -1151,188 +1332,460 @@
       <c r="F4" s="2" t="s">
         <v>3</v>
       </c>
+      <c r="G4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+      <c r="M4" s="2"/>
+      <c r="N4" s="2"/>
     </row>
-    <row r="5" customHeight="1" spans="3:6">
+    <row r="5" customHeight="1" spans="1:14">
       <c r="C5" s="2" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>6</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="K5" s="2"/>
+      <c r="L5" s="2"/>
+      <c r="M5" s="2"/>
+      <c r="N5" s="2"/>
     </row>
-    <row r="6" customHeight="1" spans="3:6">
+    <row r="6" customHeight="1" spans="1:14">
       <c r="C6" s="1">
         <v>1</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="E6" s="1">
         <v>1</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>8</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="K6" s="3"/>
+      <c r="L6" s="3"/>
+      <c r="M6" s="1"/>
+      <c r="N6" s="3"/>
     </row>
-    <row r="7" customHeight="1" spans="3:6">
+    <row r="7" customHeight="1" spans="1:14">
       <c r="C7" s="1">
         <v>2</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="E7" s="1">
         <v>1</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>10</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="J7" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="K7" s="3"/>
+      <c r="L7" s="3"/>
+      <c r="M7" s="1"/>
+      <c r="N7" s="3"/>
     </row>
-    <row r="8" customHeight="1" spans="3:6">
+    <row r="8" customHeight="1" spans="1:14">
       <c r="C8" s="1">
         <v>3</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="E8" s="1">
         <v>1</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>12</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="J8" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="K8" s="3"/>
+      <c r="L8" s="3"/>
+      <c r="M8" s="1"/>
+      <c r="N8" s="3"/>
     </row>
-    <row r="9" customHeight="1" spans="3:6">
+    <row r="9" customHeight="1" spans="1:14">
       <c r="C9" s="1">
         <v>4</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="E9" s="1">
         <v>1</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>14</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I9" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="J9" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="K9" s="3"/>
+      <c r="L9" s="3"/>
+      <c r="M9" s="1"/>
+      <c r="N9" s="3"/>
     </row>
-    <row r="10" customHeight="1" spans="3:6">
+    <row r="10" customHeight="1" spans="1:14">
+      <c r="A10" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>31</v>
+      </c>
       <c r="C10" s="1">
         <v>5</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="E10" s="1">
         <v>1</v>
       </c>
       <c r="F10" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="H10" s="4" t="s">
         <v>16</v>
       </c>
+      <c r="I10" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="J10" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="K10" s="3"/>
+      <c r="L10" s="3"/>
+      <c r="M10" s="1"/>
+      <c r="N10" s="3"/>
     </row>
-    <row r="11" customHeight="1" spans="3:6">
+    <row r="11" customHeight="1" spans="1:14">
+      <c r="A11" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>31</v>
+      </c>
       <c r="C11" s="1">
         <v>6</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="E11" s="1">
         <v>1</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>18</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I11" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="J11" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="K11" s="3"/>
+      <c r="L11" s="3"/>
+      <c r="M11" s="1"/>
+      <c r="N11" s="3"/>
     </row>
-    <row r="12" customHeight="1" spans="3:6">
+    <row r="12" customHeight="1" spans="1:14">
+      <c r="A12" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>31</v>
+      </c>
       <c r="C12" s="1">
         <v>7</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="E12" s="1">
         <v>1</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>20</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I12" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="J12" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="K12" s="3"/>
+      <c r="L12" s="3"/>
+      <c r="M12" s="1"/>
+      <c r="N12" s="3"/>
     </row>
-    <row r="13" customHeight="1" spans="3:6">
+    <row r="13" customHeight="1" spans="1:14">
+      <c r="A13" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>31</v>
+      </c>
       <c r="C13" s="1">
         <v>8</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="E13" s="1">
         <v>1</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>22</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I13" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="J13" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="K13" s="3"/>
+      <c r="L13" s="3"/>
+      <c r="M13" s="1"/>
+      <c r="N13" s="3"/>
     </row>
-    <row r="14" customHeight="1" spans="3:6">
+    <row r="14" customHeight="1" spans="1:14">
+      <c r="A14" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>31</v>
+      </c>
       <c r="C14" s="1">
         <v>9</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>23</v>
+        <v>48</v>
       </c>
       <c r="E14" s="1">
         <v>1</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>24</v>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I14" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="J14" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="K14" s="3"/>
+      <c r="L14" s="3"/>
+      <c r="M14" s="1"/>
+      <c r="N14" s="3"/>
     </row>
-    <row r="15" customHeight="1" spans="3:6">
+    <row r="15" customHeight="1" spans="1:14">
+      <c r="A15" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>31</v>
+      </c>
       <c r="C15" s="1">
         <v>10</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>25</v>
+        <v>52</v>
       </c>
       <c r="E15" s="1">
         <v>1</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>26</v>
-      </c>
+        <v>53</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I15" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="J15" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="K15" s="3"/>
+      <c r="L15" s="3"/>
+      <c r="M15" s="1"/>
+      <c r="N15" s="3"/>
     </row>
-    <row r="16" customHeight="1" spans="3:6">
+    <row r="16" customHeight="1" spans="1:14">
+      <c r="A16" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>31</v>
+      </c>
       <c r="C16" s="1">
         <v>11</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>27</v>
+        <v>56</v>
       </c>
       <c r="E16" s="1">
         <v>1</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>28</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="H16" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I16" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="J16" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="K16" s="3"/>
+      <c r="L16" s="3"/>
+      <c r="M16" s="1"/>
+      <c r="N16" s="3"/>
     </row>
-    <row r="17" customHeight="1" spans="3:6">
+    <row r="17" customHeight="1" spans="1:14">
+      <c r="A17" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>31</v>
+      </c>
       <c r="C17" s="1">
         <v>12</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="E17" s="1">
         <v>1</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>30</v>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I17" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="J17" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="K17" s="3"/>
+      <c r="L17" s="3"/>
+      <c r="M17" s="1"/>
+      <c r="N17" s="3"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="C3:C1048576">
@@ -1346,5 +1799,6 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/Excel/MapGroupConfig.xlsx
+++ b/Excel/MapGroupConfig.xlsx
@@ -1406,7 +1406,6 @@
       </c>
       <c r="K6" s="3"/>
       <c r="L6" s="3"/>
-      <c r="M6" s="1"/>
       <c r="N6" s="3"/>
     </row>
     <row r="7" customHeight="1" spans="1:14">
@@ -1436,7 +1435,6 @@
       </c>
       <c r="K7" s="3"/>
       <c r="L7" s="3"/>
-      <c r="M7" s="1"/>
       <c r="N7" s="3"/>
     </row>
     <row r="8" customHeight="1" spans="1:14">
@@ -1466,7 +1464,6 @@
       </c>
       <c r="K8" s="3"/>
       <c r="L8" s="3"/>
-      <c r="M8" s="1"/>
       <c r="N8" s="3"/>
     </row>
     <row r="9" customHeight="1" spans="1:14">
@@ -1496,7 +1493,6 @@
       </c>
       <c r="K9" s="3"/>
       <c r="L9" s="3"/>
-      <c r="M9" s="1"/>
       <c r="N9" s="3"/>
     </row>
     <row r="10" customHeight="1" spans="1:14">
@@ -1532,7 +1528,6 @@
       </c>
       <c r="K10" s="3"/>
       <c r="L10" s="3"/>
-      <c r="M10" s="1"/>
       <c r="N10" s="3"/>
     </row>
     <row r="11" customHeight="1" spans="1:14">
@@ -1568,7 +1563,6 @@
       </c>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
-      <c r="M11" s="1"/>
       <c r="N11" s="3"/>
     </row>
     <row r="12" customHeight="1" spans="1:14">
@@ -1604,7 +1598,6 @@
       </c>
       <c r="K12" s="3"/>
       <c r="L12" s="3"/>
-      <c r="M12" s="1"/>
       <c r="N12" s="3"/>
     </row>
     <row r="13" customHeight="1" spans="1:14">
@@ -1640,7 +1633,6 @@
       </c>
       <c r="K13" s="3"/>
       <c r="L13" s="3"/>
-      <c r="M13" s="1"/>
       <c r="N13" s="3"/>
     </row>
     <row r="14" customHeight="1" spans="1:14">
@@ -1676,7 +1668,6 @@
       </c>
       <c r="K14" s="3"/>
       <c r="L14" s="3"/>
-      <c r="M14" s="1"/>
       <c r="N14" s="3"/>
     </row>
     <row r="15" customHeight="1" spans="1:14">
@@ -1712,7 +1703,6 @@
       </c>
       <c r="K15" s="3"/>
       <c r="L15" s="3"/>
-      <c r="M15" s="1"/>
       <c r="N15" s="3"/>
     </row>
     <row r="16" customHeight="1" spans="1:14">
@@ -1748,7 +1738,6 @@
       </c>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
-      <c r="M16" s="1"/>
       <c r="N16" s="3"/>
     </row>
     <row r="17" customHeight="1" spans="1:14">
@@ -1784,7 +1773,6 @@
       </c>
       <c r="K17" s="3"/>
       <c r="L17" s="3"/>
-      <c r="M17" s="1"/>
       <c r="N17" s="3"/>
     </row>
   </sheetData>

--- a/Excel/MapGroupConfig.xlsx
+++ b/Excel/MapGroupConfig.xlsx
@@ -81,7 +81,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="66">
   <si>
     <t>_Id</t>
   </si>
@@ -134,10 +134,10 @@
     <t>1,1,1</t>
   </si>
   <si>
-    <t>30001,180006,20005,20006</t>
-  </si>
-  <si>
-    <t>1,1,2,2</t>
+    <t>30001,180006,20005,20006,21001</t>
+  </si>
+  <si>
+    <t>1,1,2,2,5</t>
   </si>
   <si>
     <t>幽暗沼泽</t>
@@ -149,7 +149,10 @@
     <t>2012,4004,5002</t>
   </si>
   <si>
-    <t>30001,180012,20011,20012</t>
+    <t>30001,180012,20011,20012,21002</t>
+  </si>
+  <si>
+    <t>1,1,2,2,6</t>
   </si>
   <si>
     <t>碎石矿场</t>
@@ -161,7 +164,10 @@
     <t>2018,4006,5003</t>
   </si>
   <si>
-    <t>30001,180018,20017,20018</t>
+    <t>30001,180018,20017,20018,21003</t>
+  </si>
+  <si>
+    <t>1,1,2,2,7</t>
   </si>
   <si>
     <t>枯骨荒漠</t>
@@ -173,7 +179,10 @@
     <t>2024,4007,5004</t>
   </si>
   <si>
-    <t>30001,180024,20023,20024</t>
+    <t>30001,180024,20023,20024,21004</t>
+  </si>
+  <si>
+    <t>1,1,2,2,8</t>
   </si>
   <si>
     <t>#</t>
@@ -1284,7 +1293,9 @@
     <col min="4" max="4" width="16.6363636363636" style="1" customWidth="1"/>
     <col min="5" max="5" width="16.1818181818182" style="1" customWidth="1"/>
     <col min="6" max="6" width="40.4545454545455" style="1" customWidth="1"/>
-    <col min="7" max="14" width="24.2727272727273" style="1" customWidth="1"/>
+    <col min="7" max="8" width="24.2727272727273" style="1" customWidth="1"/>
+    <col min="9" max="9" width="29.9090909090909" style="1" customWidth="1"/>
+    <col min="10" max="14" width="24.2727272727273" style="1" customWidth="1"/>
     <col min="15" max="16377" width="9.25454545454545" style="1" customWidth="1"/>
     <col min="16378" max="16384" width="9.25454545454545" style="1"/>
   </cols>
@@ -1431,7 +1442,7 @@
         <v>22</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="K7" s="3"/>
       <c r="L7" s="3"/>
@@ -1442,25 +1453,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E8" s="1">
         <v>1</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H8" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="K8" s="3"/>
       <c r="L8" s="3"/>
@@ -1471,25 +1482,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E9" s="1">
         <v>1</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H9" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="K9" s="3"/>
       <c r="L9" s="3"/>
@@ -1497,34 +1508,34 @@
     </row>
     <row r="10" customHeight="1" spans="1:14">
       <c r="A10" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C10" s="1">
         <v>5</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E10" s="1">
         <v>1</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="H10" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="K10" s="3"/>
       <c r="L10" s="3"/>
@@ -1532,22 +1543,22 @@
     </row>
     <row r="11" customHeight="1" spans="1:14">
       <c r="A11" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C11" s="1">
         <v>6</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E11" s="1">
         <v>1</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G11" s="4" t="s">
         <v>15</v>
@@ -1556,10 +1567,10 @@
         <v>16</v>
       </c>
       <c r="I11" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="J11" s="4" t="s">
         <v>39</v>
-      </c>
-      <c r="J11" s="4" t="s">
-        <v>36</v>
       </c>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
@@ -1567,34 +1578,34 @@
     </row>
     <row r="12" customHeight="1" spans="1:14">
       <c r="A12" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C12" s="1">
         <v>7</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="E12" s="1">
         <v>1</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="H12" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="J12" s="4" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="K12" s="3"/>
       <c r="L12" s="3"/>
@@ -1602,34 +1613,34 @@
     </row>
     <row r="13" customHeight="1" spans="1:14">
       <c r="A13" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C13" s="1">
         <v>8</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="E13" s="1">
         <v>1</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="H13" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="J13" s="4" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="K13" s="3"/>
       <c r="L13" s="3"/>
@@ -1637,34 +1648,34 @@
     </row>
     <row r="14" customHeight="1" spans="1:14">
       <c r="A14" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C14" s="1">
         <v>9</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="E14" s="1">
         <v>1</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="H14" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="J14" s="4" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="K14" s="3"/>
       <c r="L14" s="3"/>
@@ -1672,34 +1683,34 @@
     </row>
     <row r="15" customHeight="1" spans="1:14">
       <c r="A15" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C15" s="1">
         <v>10</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="E15" s="1">
         <v>1</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="H15" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="J15" s="4" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="K15" s="3"/>
       <c r="L15" s="3"/>
@@ -1707,34 +1718,34 @@
     </row>
     <row r="16" customHeight="1" spans="1:14">
       <c r="A16" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C16" s="1">
         <v>11</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="E16" s="1">
         <v>1</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="H16" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I16" s="5" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="J16" s="4" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
@@ -1742,22 +1753,22 @@
     </row>
     <row r="17" customHeight="1" spans="1:14">
       <c r="A17" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C17" s="1">
         <v>12</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="E17" s="1">
         <v>1</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="G17" s="4" t="s">
         <v>21</v>
@@ -1766,10 +1777,10 @@
         <v>16</v>
       </c>
       <c r="I17" s="5" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="J17" s="4" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="K17" s="3"/>
       <c r="L17" s="3"/>

--- a/Excel/MapGroupConfig.xlsx
+++ b/Excel/MapGroupConfig.xlsx
@@ -81,7 +81,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="66">
   <si>
     <t>_Id</t>
   </si>
@@ -185,22 +185,22 @@
     <t>1,1,2,2,8</t>
   </si>
   <si>
+    <t>迷雾森林</t>
+  </si>
+  <si>
+    <t>（Lv21-25）—— 幻术迷林，精灵与野兽</t>
+  </si>
+  <si>
+    <t>2005,4002,5001</t>
+  </si>
+  <si>
+    <t>30001,180005</t>
+  </si>
+  <si>
+    <t>1,1</t>
+  </si>
+  <si>
     <t>#</t>
-  </si>
-  <si>
-    <t>迷雾森林</t>
-  </si>
-  <si>
-    <t>（Lv21-25）—— 幻术迷林，精灵与野兽</t>
-  </si>
-  <si>
-    <t>2005,4002,5001</t>
-  </si>
-  <si>
-    <t>30001,180005</t>
-  </si>
-  <si>
-    <t>1,1</t>
   </si>
   <si>
     <t>熔火地穴</t>
@@ -1507,35 +1507,29 @@
       <c r="N9" s="3"/>
     </row>
     <row r="10" customHeight="1" spans="1:14">
-      <c r="A10" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>34</v>
-      </c>
       <c r="C10" s="1">
         <v>5</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E10" s="1">
         <v>1</v>
       </c>
       <c r="F10" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G10" s="4" t="s">
         <v>36</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>37</v>
       </c>
       <c r="H10" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I10" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="J10" s="4" t="s">
         <v>38</v>
-      </c>
-      <c r="J10" s="4" t="s">
-        <v>39</v>
       </c>
       <c r="K10" s="3"/>
       <c r="L10" s="3"/>
@@ -1543,10 +1537,10 @@
     </row>
     <row r="11" customHeight="1" spans="1:14">
       <c r="A11" s="1" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="C11" s="1">
         <v>6</v>
@@ -1570,7 +1564,7 @@
         <v>42</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
@@ -1578,10 +1572,10 @@
     </row>
     <row r="12" customHeight="1" spans="1:14">
       <c r="A12" s="1" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="C12" s="1">
         <v>7</v>
@@ -1605,7 +1599,7 @@
         <v>46</v>
       </c>
       <c r="J12" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K12" s="3"/>
       <c r="L12" s="3"/>
@@ -1613,10 +1607,10 @@
     </row>
     <row r="13" customHeight="1" spans="1:14">
       <c r="A13" s="1" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="C13" s="1">
         <v>8</v>
@@ -1640,7 +1634,7 @@
         <v>50</v>
       </c>
       <c r="J13" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K13" s="3"/>
       <c r="L13" s="3"/>
@@ -1648,10 +1642,10 @@
     </row>
     <row r="14" customHeight="1" spans="1:14">
       <c r="A14" s="1" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="C14" s="1">
         <v>9</v>
@@ -1675,7 +1669,7 @@
         <v>54</v>
       </c>
       <c r="J14" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K14" s="3"/>
       <c r="L14" s="3"/>
@@ -1683,10 +1677,10 @@
     </row>
     <row r="15" customHeight="1" spans="1:14">
       <c r="A15" s="1" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="C15" s="1">
         <v>10</v>
@@ -1710,7 +1704,7 @@
         <v>58</v>
       </c>
       <c r="J15" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K15" s="3"/>
       <c r="L15" s="3"/>
@@ -1718,10 +1712,10 @@
     </row>
     <row r="16" customHeight="1" spans="1:14">
       <c r="A16" s="1" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="C16" s="1">
         <v>11</v>
@@ -1745,7 +1739,7 @@
         <v>62</v>
       </c>
       <c r="J16" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
@@ -1753,10 +1747,10 @@
     </row>
     <row r="17" customHeight="1" spans="1:14">
       <c r="A17" s="1" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="C17" s="1">
         <v>12</v>
@@ -1780,7 +1774,7 @@
         <v>65</v>
       </c>
       <c r="J17" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K17" s="3"/>
       <c r="L17" s="3"/>

--- a/Excel/MapGroupConfig.xlsx
+++ b/Excel/MapGroupConfig.xlsx
@@ -81,7 +81,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="69">
   <si>
     <t>_Id</t>
   </si>
@@ -191,37 +191,46 @@
     <t>（Lv21-25）—— 幻术迷林，精灵与野兽</t>
   </si>
   <si>
-    <t>2005,4002,5001</t>
-  </si>
-  <si>
-    <t>30001,180005</t>
+    <t>2005,4002,5005</t>
+  </si>
+  <si>
+    <t>30001,180005,20029,20030,21005</t>
+  </si>
+  <si>
+    <t>1,1,2,2,9</t>
+  </si>
+  <si>
+    <t>#</t>
+  </si>
+  <si>
+    <t>熔火地穴</t>
+  </si>
+  <si>
+    <t>（Lv26-30）—— 岩浆河流，火焰恶魔</t>
+  </si>
+  <si>
+    <t>2006,4002,5006</t>
+  </si>
+  <si>
+    <t>30001,180006,20035,20036,21006</t>
+  </si>
+  <si>
+    <t>1,1,2,2,10</t>
+  </si>
+  <si>
+    <t>雷光废墟</t>
+  </si>
+  <si>
+    <t>（Lv31-35）—— 古代魔法遗迹，雷电元素</t>
+  </si>
+  <si>
+    <t>2007,4003,5002</t>
+  </si>
+  <si>
+    <t>30001,180007</t>
   </si>
   <si>
     <t>1,1</t>
-  </si>
-  <si>
-    <t>#</t>
-  </si>
-  <si>
-    <t>熔火地穴</t>
-  </si>
-  <si>
-    <t>（Lv26-30）—— 岩浆河流，火焰恶魔</t>
-  </si>
-  <si>
-    <t>30001,180006</t>
-  </si>
-  <si>
-    <t>雷光废墟</t>
-  </si>
-  <si>
-    <t>（Lv31-35）—— 古代魔法遗迹，雷电元素</t>
-  </si>
-  <si>
-    <t>2007,4003,5002</t>
-  </si>
-  <si>
-    <t>30001,180007</t>
   </si>
   <si>
     <t>冰封王陵</t>
@@ -1555,16 +1564,16 @@
         <v>41</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="H11" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
@@ -1581,25 +1590,25 @@
         <v>7</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E12" s="1">
         <v>1</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H12" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="J12" s="4" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="K12" s="3"/>
       <c r="L12" s="3"/>
@@ -1616,25 +1625,25 @@
         <v>8</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E13" s="1">
         <v>1</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="H13" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="J13" s="4" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="K13" s="3"/>
       <c r="L13" s="3"/>
@@ -1651,25 +1660,25 @@
         <v>9</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E14" s="1">
         <v>1</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="H14" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="J14" s="4" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="K14" s="3"/>
       <c r="L14" s="3"/>
@@ -1686,25 +1695,25 @@
         <v>10</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="E15" s="1">
         <v>1</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="H15" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="J15" s="4" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="K15" s="3"/>
       <c r="L15" s="3"/>
@@ -1721,25 +1730,25 @@
         <v>11</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="E16" s="1">
         <v>1</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="H16" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I16" s="5" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="J16" s="4" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
@@ -1756,13 +1765,13 @@
         <v>12</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="E17" s="1">
         <v>1</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="G17" s="4" t="s">
         <v>21</v>
@@ -1771,10 +1780,10 @@
         <v>16</v>
       </c>
       <c r="I17" s="5" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="J17" s="4" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="K17" s="3"/>
       <c r="L17" s="3"/>

--- a/Excel/MapGroupConfig.xlsx
+++ b/Excel/MapGroupConfig.xlsx
@@ -81,7 +81,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="69">
   <si>
     <t>_Id</t>
   </si>
@@ -200,22 +200,22 @@
     <t>1,1,2,2,9</t>
   </si>
   <si>
+    <t>熔火地穴</t>
+  </si>
+  <si>
+    <t>（Lv26-30）—— 岩浆河流，火焰恶魔</t>
+  </si>
+  <si>
+    <t>2006,4002,5006</t>
+  </si>
+  <si>
+    <t>30001,180006,20035,20036,21006</t>
+  </si>
+  <si>
+    <t>1,1,2,2,10</t>
+  </si>
+  <si>
     <t>#</t>
-  </si>
-  <si>
-    <t>熔火地穴</t>
-  </si>
-  <si>
-    <t>（Lv26-30）—— 岩浆河流，火焰恶魔</t>
-  </si>
-  <si>
-    <t>2006,4002,5006</t>
-  </si>
-  <si>
-    <t>30001,180006,20035,20036,21006</t>
-  </si>
-  <si>
-    <t>1,1,2,2,10</t>
   </si>
   <si>
     <t>雷光废墟</t>
@@ -1545,35 +1545,29 @@
       <c r="N10" s="3"/>
     </row>
     <row r="11" customHeight="1" spans="1:14">
-      <c r="A11" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>39</v>
-      </c>
       <c r="C11" s="1">
         <v>6</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E11" s="1">
         <v>1</v>
       </c>
       <c r="F11" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="G11" s="4" t="s">
         <v>41</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>42</v>
       </c>
       <c r="H11" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I11" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="J11" s="4" t="s">
         <v>43</v>
-      </c>
-      <c r="J11" s="4" t="s">
-        <v>44</v>
       </c>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
@@ -1581,10 +1575,10 @@
     </row>
     <row r="12" customHeight="1" spans="1:14">
       <c r="A12" s="1" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="C12" s="1">
         <v>7</v>
@@ -1616,10 +1610,10 @@
     </row>
     <row r="13" customHeight="1" spans="1:14">
       <c r="A13" s="1" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="C13" s="1">
         <v>8</v>
@@ -1651,10 +1645,10 @@
     </row>
     <row r="14" customHeight="1" spans="1:14">
       <c r="A14" s="1" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="C14" s="1">
         <v>9</v>
@@ -1686,10 +1680,10 @@
     </row>
     <row r="15" customHeight="1" spans="1:14">
       <c r="A15" s="1" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="C15" s="1">
         <v>10</v>
@@ -1721,10 +1715,10 @@
     </row>
     <row r="16" customHeight="1" spans="1:14">
       <c r="A16" s="1" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="C16" s="1">
         <v>11</v>
@@ -1756,10 +1750,10 @@
     </row>
     <row r="17" customHeight="1" spans="1:14">
       <c r="A17" s="1" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="C17" s="1">
         <v>12</v>

--- a/Excel/MapGroupConfig.xlsx
+++ b/Excel/MapGroupConfig.xlsx
@@ -170,7 +170,7 @@
     <t>1,1,2,2,7</t>
   </si>
   <si>
-    <t>枯骨荒漠</t>
+    <t>迷雾森林</t>
   </si>
   <si>
     <t>（Lv16-20）—— 干旱沙海，亡灵与骸骨</t>
@@ -185,7 +185,7 @@
     <t>1,1,2,2,8</t>
   </si>
   <si>
-    <t>迷雾森林</t>
+    <t>亡者荒漠</t>
   </si>
   <si>
     <t>（Lv21-25）—— 幻术迷林，精灵与野兽</t>
@@ -200,7 +200,7 @@
     <t>1,1,2,2,9</t>
   </si>
   <si>
-    <t>熔火地穴</t>
+    <t>蛮鬃林地</t>
   </si>
   <si>
     <t>（Lv26-30）—— 岩浆河流，火焰恶魔</t>
@@ -218,7 +218,7 @@
     <t>#</t>
   </si>
   <si>
-    <t>雷光废墟</t>
+    <t>熔岩地穴</t>
   </si>
   <si>
     <t>（Lv31-35）—— 古代魔法遗迹，雷电元素</t>
@@ -245,7 +245,7 @@
     <t>30001,180008</t>
   </si>
   <si>
-    <t>诅咒祭坛</t>
+    <t>暗影祭坛</t>
   </si>
   <si>
     <t>（Lv41-45）—— 邪教圣地，高阶恶魔</t>
@@ -257,21 +257,21 @@
     <t>30001,180009</t>
   </si>
   <si>
+    <t>蛮族之地</t>
+  </si>
+  <si>
+    <t>（Lv46-50）—— 空间扭曲，异界生物</t>
+  </si>
+  <si>
+    <t>2010,4004,5002</t>
+  </si>
+  <si>
+    <t>30001,180010</t>
+  </si>
+  <si>
     <t>虚空裂谷</t>
   </si>
   <si>
-    <t>（Lv46-50）—— 空间扭曲，异界生物</t>
-  </si>
-  <si>
-    <t>2010,4004,5002</t>
-  </si>
-  <si>
-    <t>30001,180010</t>
-  </si>
-  <si>
-    <t>龙眠之地</t>
-  </si>
-  <si>
     <t>（Lv51-55）—— 远古龙巢，龙族与亚龙</t>
   </si>
   <si>
@@ -281,7 +281,7 @@
     <t>30001,180011</t>
   </si>
   <si>
-    <t>永恒神界</t>
+    <t>地狱烈焰</t>
   </si>
   <si>
     <t>（Lv56-60）—— 失落神域，法则化身</t>

--- a/Excel/MapGroupConfig.xlsx
+++ b/Excel/MapGroupConfig.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\legend2\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowHeight="17680"/>
   </bookViews>
@@ -173,7 +178,7 @@
     <t>迷雾森林</t>
   </si>
   <si>
-    <t>（Lv16-20）—— 干旱沙海，亡灵与骸骨</t>
+    <t>（Lv16-20）—— 幻术迷林，精灵与野兽</t>
   </si>
   <si>
     <t>2024,4007,5004</t>
@@ -188,7 +193,7 @@
     <t>亡者荒漠</t>
   </si>
   <si>
-    <t>（Lv21-25）—— 幻术迷林，精灵与野兽</t>
+    <t>（Lv21-25）—— 干旱沙海，亡灵与骸骨</t>
   </si>
   <si>
     <t>2005,4002,5005</t>

--- a/Excel/MapGroupConfig.xlsx
+++ b/Excel/MapGroupConfig.xlsx
@@ -86,7 +86,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="70">
   <si>
     <t>_Id</t>
   </si>
@@ -133,10 +133,10 @@
     <t>（Lv1-5）—— 荒芜草原，小野兽与游荡亡灵</t>
   </si>
   <si>
-    <t>2006,4002,5001</t>
-  </si>
-  <si>
-    <t>1,1,1</t>
+    <t>2006,4002,5001,3001</t>
+  </si>
+  <si>
+    <t>1,1,1,1</t>
   </si>
   <si>
     <t>30001,180006,20005,20006,21001</t>
@@ -151,7 +151,7 @@
     <t>（Lv6-10）—— 毒雾弥漫，虫蚁与腐生怪</t>
   </si>
   <si>
-    <t>2012,4004,5002</t>
+    <t>2012,4004,5002,3001</t>
   </si>
   <si>
     <t>30001,180012,20011,20012,21002</t>
@@ -166,13 +166,13 @@
     <t>（Lv11-15）—— 废弃矿洞，傀儡与矿工变种</t>
   </si>
   <si>
-    <t>2018,4006,5003</t>
+    <t>2018,4006,5003,3002</t>
   </si>
   <si>
     <t>30001,180018,20017,20018,21003</t>
   </si>
   <si>
-    <t>1,1,2,2,7</t>
+    <t>1,1,2,2,7,10</t>
   </si>
   <si>
     <t>迷雾森林</t>
@@ -181,13 +181,13 @@
     <t>（Lv16-20）—— 幻术迷林，精灵与野兽</t>
   </si>
   <si>
-    <t>2024,4007,5004</t>
+    <t>2024,4007,5004,3002</t>
   </si>
   <si>
     <t>30001,180024,20023,20024,21004</t>
   </si>
   <si>
-    <t>1,1,2,2,8</t>
+    <t>1,1,2,2,8,10</t>
   </si>
   <si>
     <t>亡者荒漠</t>
@@ -196,13 +196,13 @@
     <t>（Lv21-25）—— 干旱沙海，亡灵与骸骨</t>
   </si>
   <si>
-    <t>2005,4002,5005</t>
+    <t>2005,4002,5005,3003</t>
   </si>
   <si>
     <t>30001,180005,20029,20030,21005</t>
   </si>
   <si>
-    <t>1,1,2,2,9</t>
+    <t>1,1,2,2,9,10</t>
   </si>
   <si>
     <t>蛮鬃林地</t>
@@ -211,13 +211,13 @@
     <t>（Lv26-30）—— 岩浆河流，火焰恶魔</t>
   </si>
   <si>
-    <t>2006,4002,5006</t>
+    <t>2006,4002,5006,3003</t>
   </si>
   <si>
     <t>30001,180006,20035,20036,21006</t>
   </si>
   <si>
-    <t>1,1,2,2,10</t>
+    <t>1,1,2,2,10,10</t>
   </si>
   <si>
     <t>#</t>
@@ -229,7 +229,7 @@
     <t>（Lv31-35）—— 古代魔法遗迹，雷电元素</t>
   </si>
   <si>
-    <t>2007,4003,5002</t>
+    <t>2007,4003,5002,3004</t>
   </si>
   <si>
     <t>30001,180007</t>
@@ -244,7 +244,7 @@
     <t>（Lv36-40）—— 永冻墓场，冰霜亡灵</t>
   </si>
   <si>
-    <t>2008,4003,5002</t>
+    <t>2008,4003,5002,3004</t>
   </si>
   <si>
     <t>30001,180008</t>
@@ -256,7 +256,7 @@
     <t>（Lv41-45）—— 邪教圣地，高阶恶魔</t>
   </si>
   <si>
-    <t>2009,4003,5002</t>
+    <t>2009,4003,5002,3004</t>
   </si>
   <si>
     <t>30001,180009</t>
@@ -268,7 +268,7 @@
     <t>（Lv46-50）—— 空间扭曲，异界生物</t>
   </si>
   <si>
-    <t>2010,4004,5002</t>
+    <t>2010,4004,5002,3004</t>
   </si>
   <si>
     <t>30001,180010</t>
@@ -280,7 +280,7 @@
     <t>（Lv51-55）—— 远古龙巢，龙族与亚龙</t>
   </si>
   <si>
-    <t>2011,4004,5002</t>
+    <t>2011,4004,5002,3004</t>
   </si>
   <si>
     <t>30001,180011</t>
@@ -290,6 +290,9 @@
   </si>
   <si>
     <t>（Lv56-60）—— 失落神域，法则化身</t>
+  </si>
+  <si>
+    <t>2012,4004,5002,3004</t>
   </si>
   <si>
     <t>30001,180012</t>
@@ -1308,7 +1311,7 @@
     <col min="5" max="5" width="16.1818181818182" style="1" customWidth="1"/>
     <col min="6" max="6" width="40.4545454545455" style="1" customWidth="1"/>
     <col min="7" max="8" width="24.2727272727273" style="1" customWidth="1"/>
-    <col min="9" max="9" width="29.9090909090909" style="1" customWidth="1"/>
+    <col min="9" max="9" width="33.6363636363636" style="1" customWidth="1"/>
     <col min="10" max="14" width="24.2727272727273" style="1" customWidth="1"/>
     <col min="15" max="16377" width="9.25454545454545" style="1" customWidth="1"/>
     <col min="16378" max="16384" width="9.25454545454545" style="1"/>
@@ -1773,13 +1776,13 @@
         <v>67</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>21</v>
+        <v>68</v>
       </c>
       <c r="H17" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I17" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J17" s="4" t="s">
         <v>49</v>

--- a/Excel/MapGroupConfig.xlsx
+++ b/Excel/MapGroupConfig.xlsx
@@ -86,7 +86,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="71">
   <si>
     <t>_Id</t>
   </si>
@@ -196,10 +196,10 @@
     <t>（Lv21-25）—— 干旱沙海，亡灵与骸骨</t>
   </si>
   <si>
-    <t>2005,4002,5005,3003</t>
-  </si>
-  <si>
-    <t>30001,180005,20029,20030,21005</t>
+    <t>2005,4007,5005,3003</t>
+  </si>
+  <si>
+    <t>30001,180030,20029,20030,21005</t>
   </si>
   <si>
     <t>1,1,2,2,9,10</t>
@@ -211,43 +211,40 @@
     <t>（Lv26-30）—— 岩浆河流，火焰恶魔</t>
   </si>
   <si>
-    <t>2006,4002,5006,3003</t>
-  </si>
-  <si>
-    <t>30001,180006,20035,20036,21006</t>
+    <t>2006,4007,5006,3003</t>
+  </si>
+  <si>
+    <t>30001,180036,20035,20036,21006</t>
   </si>
   <si>
     <t>1,1,2,2,10,10</t>
   </si>
   <si>
+    <t>熔岩地穴</t>
+  </si>
+  <si>
+    <t>（Lv31-35）—— 古代魔法遗迹，雷电元素</t>
+  </si>
+  <si>
+    <t>2007,4007,5007,3004</t>
+  </si>
+  <si>
+    <t>30001,180042,20041,20042,21007</t>
+  </si>
+  <si>
     <t>#</t>
   </si>
   <si>
-    <t>熔岩地穴</t>
-  </si>
-  <si>
-    <t>（Lv31-35）—— 古代魔法遗迹，雷电元素</t>
-  </si>
-  <si>
-    <t>2007,4003,5002,3004</t>
-  </si>
-  <si>
-    <t>30001,180007</t>
-  </si>
-  <si>
-    <t>1,1</t>
-  </si>
-  <si>
     <t>冰封王陵</t>
   </si>
   <si>
     <t>（Lv36-40）—— 永冻墓场，冰霜亡灵</t>
   </si>
   <si>
-    <t>2008,4003,5002,3004</t>
-  </si>
-  <si>
-    <t>30001,180008</t>
+    <t>2008,4007,5008,3004</t>
+  </si>
+  <si>
+    <t>30001,180048,20047,20048,21008</t>
   </si>
   <si>
     <t>暗影祭坛</t>
@@ -256,10 +253,10 @@
     <t>（Lv41-45）—— 邪教圣地，高阶恶魔</t>
   </si>
   <si>
-    <t>2009,4003,5002,3004</t>
-  </si>
-  <si>
-    <t>30001,180009</t>
+    <t>2009,4007,5009,3004</t>
+  </si>
+  <si>
+    <t>30001,180054,20053,20054,21009</t>
   </si>
   <si>
     <t>蛮族之地</t>
@@ -268,10 +265,10 @@
     <t>（Lv46-50）—— 空间扭曲，异界生物</t>
   </si>
   <si>
-    <t>2010,4004,5002,3004</t>
-  </si>
-  <si>
-    <t>30001,180010</t>
+    <t>2010,4007,5010,3004</t>
+  </si>
+  <si>
+    <t>30001,180060,20059,20060,21010</t>
   </si>
   <si>
     <t>虚空裂谷</t>
@@ -280,10 +277,10 @@
     <t>（Lv51-55）—— 远古龙巢，龙族与亚龙</t>
   </si>
   <si>
-    <t>2011,4004,5002,3004</t>
-  </si>
-  <si>
-    <t>30001,180011</t>
+    <t>2011,4007,5011,3004</t>
+  </si>
+  <si>
+    <t>30001,180066,20065,20066,21011</t>
   </si>
   <si>
     <t>地狱烈焰</t>
@@ -292,10 +289,16 @@
     <t>（Lv56-60）—— 失落神域，法则化身</t>
   </si>
   <si>
-    <t>2012,4004,5002,3004</t>
-  </si>
-  <si>
-    <t>30001,180012</t>
+    <t>2012,4007,5012,3004</t>
+  </si>
+  <si>
+    <t>30001,180072,20071,20072,21012</t>
+  </si>
+  <si>
+    <t>装备，技能，珍宝，神兵符</t>
+  </si>
+  <si>
+    <t>四格，宠物，衣服，武器，传奇装备</t>
   </si>
 </sst>
 </file>
@@ -474,12 +477,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1303,7 +1306,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:N17"/>
+  <dimension ref="A3:N30"/>
   <sheetFormatPr defaultColWidth="9.25454545454545" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9.25454545454545" style="1" customWidth="1"/>
@@ -1582,35 +1585,29 @@
       <c r="N11" s="3"/>
     </row>
     <row r="12" customHeight="1" spans="1:14">
-      <c r="A12" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>44</v>
-      </c>
       <c r="C12" s="1">
         <v>7</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E12" s="1">
         <v>1</v>
       </c>
       <c r="F12" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G12" s="4" t="s">
         <v>46</v>
-      </c>
-      <c r="G12" s="4" t="s">
-        <v>47</v>
       </c>
       <c r="H12" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J12" s="4" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="K12" s="3"/>
       <c r="L12" s="3"/>
@@ -1618,34 +1615,34 @@
     </row>
     <row r="13" customHeight="1" spans="1:14">
       <c r="A13" s="1" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="C13" s="1">
         <v>8</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E13" s="1">
         <v>1</v>
       </c>
       <c r="F13" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="G13" s="4" t="s">
         <v>51</v>
-      </c>
-      <c r="G13" s="4" t="s">
-        <v>52</v>
       </c>
       <c r="H13" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J13" s="4" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="K13" s="3"/>
       <c r="L13" s="3"/>
@@ -1653,34 +1650,34 @@
     </row>
     <row r="14" customHeight="1" spans="1:14">
       <c r="A14" s="1" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="C14" s="1">
         <v>9</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E14" s="1">
         <v>1</v>
       </c>
       <c r="F14" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="G14" s="4" t="s">
         <v>55</v>
-      </c>
-      <c r="G14" s="4" t="s">
-        <v>56</v>
       </c>
       <c r="H14" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J14" s="4" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="K14" s="3"/>
       <c r="L14" s="3"/>
@@ -1688,34 +1685,34 @@
     </row>
     <row r="15" customHeight="1" spans="1:14">
       <c r="A15" s="1" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="C15" s="1">
         <v>10</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E15" s="1">
         <v>1</v>
       </c>
       <c r="F15" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="G15" s="4" t="s">
         <v>59</v>
-      </c>
-      <c r="G15" s="4" t="s">
-        <v>60</v>
       </c>
       <c r="H15" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J15" s="4" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="K15" s="3"/>
       <c r="L15" s="3"/>
@@ -1723,34 +1720,34 @@
     </row>
     <row r="16" customHeight="1" spans="1:14">
       <c r="A16" s="1" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="C16" s="1">
         <v>11</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E16" s="1">
         <v>1</v>
       </c>
       <c r="F16" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="G16" s="4" t="s">
         <v>63</v>
-      </c>
-      <c r="G16" s="4" t="s">
-        <v>64</v>
       </c>
       <c r="H16" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I16" s="5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J16" s="4" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
@@ -1758,38 +1755,54 @@
     </row>
     <row r="17" customHeight="1" spans="1:14">
       <c r="A17" s="1" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="C17" s="1">
         <v>12</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E17" s="1">
         <v>1</v>
       </c>
       <c r="F17" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="G17" s="4" t="s">
         <v>67</v>
-      </c>
-      <c r="G17" s="4" t="s">
-        <v>68</v>
       </c>
       <c r="H17" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I17" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="J17" s="4" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="K17" s="3"/>
       <c r="L17" s="3"/>
       <c r="N17" s="3"/>
+    </row>
+    <row r="29" customHeight="1" spans="1:14">
+      <c r="G29" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="I29" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="30" customHeight="1" spans="1:14">
+      <c r="A30" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>48</v>
+      </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="C3:C1048576">

--- a/Excel/MapGroupConfig.xlsx
+++ b/Excel/MapGroupConfig.xlsx
@@ -477,12 +477,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>

--- a/Excel/MapGroupConfig.xlsx
+++ b/Excel/MapGroupConfig.xlsx
@@ -229,7 +229,7 @@
     <t>2007,4007,5007,3004</t>
   </si>
   <si>
-    <t>30001,180042,20041,20042,21007</t>
+    <t>30001,180042,20041,20042,21006</t>
   </si>
   <si>
     <t>#</t>
@@ -244,7 +244,7 @@
     <t>2008,4007,5008,3004</t>
   </si>
   <si>
-    <t>30001,180048,20047,20048,21008</t>
+    <t>30001,180048,20047,20048,21004</t>
   </si>
   <si>
     <t>暗影祭坛</t>
@@ -256,7 +256,7 @@
     <t>2009,4007,5009,3004</t>
   </si>
   <si>
-    <t>30001,180054,20053,20054,21009</t>
+    <t>30001,180054,20053,20054,21005</t>
   </si>
   <si>
     <t>蛮族之地</t>
@@ -268,7 +268,7 @@
     <t>2010,4007,5010,3004</t>
   </si>
   <si>
-    <t>30001,180060,20059,20060,21010</t>
+    <t>30001,180060,20059,20060,21006</t>
   </si>
   <si>
     <t>虚空裂谷</t>
@@ -280,7 +280,7 @@
     <t>2011,4007,5011,3004</t>
   </si>
   <si>
-    <t>30001,180066,20065,20066,21011</t>
+    <t>30001,180066,20065,20066,21006</t>
   </si>
   <si>
     <t>地狱烈焰</t>
@@ -292,7 +292,7 @@
     <t>2012,4007,5012,3004</t>
   </si>
   <si>
-    <t>30001,180072,20071,20072,21012</t>
+    <t>30001,180072,20071,20072,21006</t>
   </si>
   <si>
     <t>装备，技能，珍宝，神兵符</t>

--- a/Excel/MapGroupConfig.xlsx
+++ b/Excel/MapGroupConfig.xlsx
@@ -38,28 +38,6 @@
   </authors>
   <commentList>
     <comment ref="G3" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>admin:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-组合掉落</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="K3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -1311,11 +1289,16 @@
   <cols>
     <col min="1" max="3" width="9.25454545454545" style="1" customWidth="1"/>
     <col min="4" max="4" width="16.6363636363636" style="1" customWidth="1"/>
-    <col min="5" max="5" width="16.1818181818182" style="1" customWidth="1"/>
+    <col min="5" max="5" width="13" style="1" customWidth="1"/>
     <col min="6" max="6" width="40.4545454545455" style="1" customWidth="1"/>
-    <col min="7" max="8" width="24.2727272727273" style="1" customWidth="1"/>
+    <col min="7" max="7" width="24.2727272727273" style="1" customWidth="1"/>
+    <col min="8" max="8" width="21.0909090909091" style="1" customWidth="1"/>
     <col min="9" max="9" width="33.6363636363636" style="1" customWidth="1"/>
-    <col min="10" max="14" width="24.2727272727273" style="1" customWidth="1"/>
+    <col min="10" max="10" width="24.2727272727273" style="1" customWidth="1"/>
+    <col min="11" max="11" width="12.9090909090909" style="1" customWidth="1"/>
+    <col min="12" max="12" width="12" style="1" customWidth="1"/>
+    <col min="13" max="13" width="10.0909090909091" style="1" customWidth="1"/>
+    <col min="14" max="14" width="24.2727272727273" style="1" customWidth="1"/>
     <col min="15" max="16377" width="9.25454545454545" style="1" customWidth="1"/>
     <col min="16378" max="16384" width="9.25454545454545" style="1"/>
   </cols>

--- a/Excel/MapGroupConfig.xlsx
+++ b/Excel/MapGroupConfig.xlsx
@@ -111,7 +111,7 @@
     <t>（Lv1-5）—— 荒芜草原，小野兽与游荡亡灵</t>
   </si>
   <si>
-    <t>2006,4002,5001,3001</t>
+    <t>2006,4002,5001,3002</t>
   </si>
   <si>
     <t>1,1,1,1</t>
@@ -129,7 +129,7 @@
     <t>（Lv6-10）—— 毒雾弥漫，虫蚁与腐生怪</t>
   </si>
   <si>
-    <t>2012,4004,5002,3001</t>
+    <t>2012,4004,5002,3003</t>
   </si>
   <si>
     <t>30001,180012,20011,20012,21002</t>
@@ -144,7 +144,7 @@
     <t>（Lv11-15）—— 废弃矿洞，傀儡与矿工变种</t>
   </si>
   <si>
-    <t>2018,4006,5003,3002</t>
+    <t>2018,4006,5003,3004</t>
   </si>
   <si>
     <t>30001,180018,20017,20018,21003</t>
@@ -159,7 +159,7 @@
     <t>（Lv16-20）—— 幻术迷林，精灵与野兽</t>
   </si>
   <si>
-    <t>2024,4007,5004,3002</t>
+    <t>2024,4007,5004,3004</t>
   </si>
   <si>
     <t>30001,180024,20023,20024,21004</t>
@@ -174,7 +174,7 @@
     <t>（Lv21-25）—— 干旱沙海，亡灵与骸骨</t>
   </si>
   <si>
-    <t>2005,4007,5005,3003</t>
+    <t>2005,4007,5005,3004</t>
   </si>
   <si>
     <t>30001,180030,20029,20030,21005</t>
@@ -189,7 +189,7 @@
     <t>（Lv26-30）—— 岩浆河流，火焰恶魔</t>
   </si>
   <si>
-    <t>2006,4007,5006,3003</t>
+    <t>2006,4007,5006,3004</t>
   </si>
   <si>
     <t>30001,180036,20035,20036,21006</t>

--- a/Excel/MapGroupConfig.xlsx
+++ b/Excel/MapGroupConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView windowWidth="25600" windowHeight="11480"/>
   </bookViews>
   <sheets>
     <sheet name="UnitProto" sheetId="1" r:id="rId1"/>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="71">
   <si>
     <t>_Id</t>
   </si>
@@ -210,43 +210,43 @@
     <t>30001,180042,20041,20042,21006</t>
   </si>
   <si>
+    <t>冰封王陵</t>
+  </si>
+  <si>
+    <t>（Lv36-40）—— 永冻墓场，冰霜亡灵</t>
+  </si>
+  <si>
+    <t>2008,4007,5008,3004</t>
+  </si>
+  <si>
+    <t>30001,180048,20047,20048,21004</t>
+  </si>
+  <si>
+    <t>暗影祭坛</t>
+  </si>
+  <si>
+    <t>（Lv41-45）—— 邪教圣地，高阶恶魔</t>
+  </si>
+  <si>
+    <t>2009,4007,5009,3004</t>
+  </si>
+  <si>
+    <t>30001,180054,20053,20054,21005</t>
+  </si>
+  <si>
+    <t>蛮族之地</t>
+  </si>
+  <si>
+    <t>（Lv46-50）—— 空间扭曲，异界生物</t>
+  </si>
+  <si>
+    <t>2010,4007,5010,3004</t>
+  </si>
+  <si>
+    <t>30001,180060,20059,20060,21006</t>
+  </si>
+  <si>
     <t>#</t>
-  </si>
-  <si>
-    <t>冰封王陵</t>
-  </si>
-  <si>
-    <t>（Lv36-40）—— 永冻墓场，冰霜亡灵</t>
-  </si>
-  <si>
-    <t>2008,4007,5008,3004</t>
-  </si>
-  <si>
-    <t>30001,180048,20047,20048,21004</t>
-  </si>
-  <si>
-    <t>暗影祭坛</t>
-  </si>
-  <si>
-    <t>（Lv41-45）—— 邪教圣地，高阶恶魔</t>
-  </si>
-  <si>
-    <t>2009,4007,5009,3004</t>
-  </si>
-  <si>
-    <t>30001,180054,20053,20054,21005</t>
-  </si>
-  <si>
-    <t>蛮族之地</t>
-  </si>
-  <si>
-    <t>（Lv46-50）—— 空间扭曲，异界生物</t>
-  </si>
-  <si>
-    <t>2010,4007,5010,3004</t>
-  </si>
-  <si>
-    <t>30001,180060,20059,20060,21006</t>
   </si>
   <si>
     <t>虚空裂谷</t>
@@ -1285,9 +1285,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A3:N30"/>
-  <sheetFormatPr defaultColWidth="9.25454545454545" defaultRowHeight="18" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="9.27272727272727" defaultRowHeight="18" customHeight="1"/>
   <cols>
-    <col min="1" max="3" width="9.25454545454545" style="1" customWidth="1"/>
+    <col min="1" max="3" width="9.27272727272727" style="1" customWidth="1"/>
     <col min="4" max="4" width="16.6363636363636" style="1" customWidth="1"/>
     <col min="5" max="5" width="13" style="1" customWidth="1"/>
     <col min="6" max="6" width="40.4545454545455" style="1" customWidth="1"/>
@@ -1299,8 +1299,8 @@
     <col min="12" max="12" width="12" style="1" customWidth="1"/>
     <col min="13" max="13" width="10.0909090909091" style="1" customWidth="1"/>
     <col min="14" max="14" width="24.2727272727273" style="1" customWidth="1"/>
-    <col min="15" max="16377" width="9.25454545454545" style="1" customWidth="1"/>
-    <col min="16378" max="16384" width="9.25454545454545" style="1"/>
+    <col min="15" max="16377" width="9.27272727272727" style="1" customWidth="1"/>
+    <col min="16378" max="16384" width="9.27272727272727" style="1"/>
   </cols>
   <sheetData>
     <row r="3" customHeight="1" spans="1:14">
@@ -1597,32 +1597,26 @@
       <c r="N12" s="3"/>
     </row>
     <row r="13" customHeight="1" spans="1:14">
-      <c r="A13" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="C13" s="1">
         <v>8</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E13" s="1">
         <v>1</v>
       </c>
       <c r="F13" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="G13" s="4" t="s">
         <v>50</v>
-      </c>
-      <c r="G13" s="4" t="s">
-        <v>51</v>
       </c>
       <c r="H13" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="J13" s="4" t="s">
         <v>43</v>
@@ -1632,32 +1626,26 @@
       <c r="N13" s="3"/>
     </row>
     <row r="14" customHeight="1" spans="1:14">
-      <c r="A14" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="C14" s="1">
         <v>9</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E14" s="1">
         <v>1</v>
       </c>
       <c r="F14" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="G14" s="4" t="s">
         <v>54</v>
-      </c>
-      <c r="G14" s="4" t="s">
-        <v>55</v>
       </c>
       <c r="H14" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="J14" s="4" t="s">
         <v>43</v>
@@ -1667,32 +1655,26 @@
       <c r="N14" s="3"/>
     </row>
     <row r="15" customHeight="1" spans="1:14">
-      <c r="A15" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="C15" s="1">
         <v>10</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E15" s="1">
         <v>1</v>
       </c>
       <c r="F15" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="G15" s="4" t="s">
         <v>58</v>
-      </c>
-      <c r="G15" s="4" t="s">
-        <v>59</v>
       </c>
       <c r="H15" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="J15" s="4" t="s">
         <v>43</v>
@@ -1703,10 +1685,10 @@
     </row>
     <row r="16" customHeight="1" spans="1:14">
       <c r="A16" s="1" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="C16" s="1">
         <v>11</v>
@@ -1738,10 +1720,10 @@
     </row>
     <row r="17" customHeight="1" spans="1:14">
       <c r="A17" s="1" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="C17" s="1">
         <v>12</v>
@@ -1781,10 +1763,10 @@
     </row>
     <row r="30" customHeight="1" spans="1:14">
       <c r="A30" s="1" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/MapGroupConfig.xlsx
+++ b/Excel/MapGroupConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="11480"/>
+    <workbookView windowWidth="25600" windowHeight="12080"/>
   </bookViews>
   <sheets>
     <sheet name="UnitProto" sheetId="1" r:id="rId1"/>
@@ -174,7 +174,7 @@
     <t>（Lv21-25）—— 干旱沙海，亡灵与骸骨</t>
   </si>
   <si>
-    <t>2005,4007,5005,3004</t>
+    <t>2030,4007,5005,3004</t>
   </si>
   <si>
     <t>30001,180030,20029,20030,21005</t>
@@ -189,7 +189,7 @@
     <t>（Lv26-30）—— 岩浆河流，火焰恶魔</t>
   </si>
   <si>
-    <t>2006,4007,5006,3004</t>
+    <t>2036,4007,5006,3004</t>
   </si>
   <si>
     <t>30001,180036,20035,20036,21006</t>
@@ -204,10 +204,10 @@
     <t>（Lv31-35）—— 古代魔法遗迹，雷电元素</t>
   </si>
   <si>
-    <t>2007,4007,5007,3004</t>
-  </si>
-  <si>
-    <t>30001,180042,20041,20042,21006</t>
+    <t>2042,4007,5007,3004</t>
+  </si>
+  <si>
+    <t>30001,180042,20041,20042,21007</t>
   </si>
   <si>
     <t>冰封王陵</t>
@@ -216,10 +216,10 @@
     <t>（Lv36-40）—— 永冻墓场，冰霜亡灵</t>
   </si>
   <si>
-    <t>2008,4007,5008,3004</t>
-  </si>
-  <si>
-    <t>30001,180048,20047,20048,21004</t>
+    <t>2048,4007,5008,3004</t>
+  </si>
+  <si>
+    <t>30001,180048,20047,20048,21008</t>
   </si>
   <si>
     <t>暗影祭坛</t>
@@ -228,10 +228,10 @@
     <t>（Lv41-45）—— 邪教圣地，高阶恶魔</t>
   </si>
   <si>
-    <t>2009,4007,5009,3004</t>
-  </si>
-  <si>
-    <t>30001,180054,20053,20054,21005</t>
+    <t>2054,4007,5009,3004</t>
+  </si>
+  <si>
+    <t>30001,180054,20053,20054,21008</t>
   </si>
   <si>
     <t>蛮族之地</t>
@@ -240,10 +240,10 @@
     <t>（Lv46-50）—— 空间扭曲，异界生物</t>
   </si>
   <si>
-    <t>2010,4007,5010,3004</t>
-  </si>
-  <si>
-    <t>30001,180060,20059,20060,21006</t>
+    <t>2060,4007,5010,3004</t>
+  </si>
+  <si>
+    <t>30001,180060,20059,20060,21008</t>
   </si>
   <si>
     <t>#</t>
@@ -255,10 +255,10 @@
     <t>（Lv51-55）—— 远古龙巢，龙族与亚龙</t>
   </si>
   <si>
-    <t>2011,4007,5011,3004</t>
-  </si>
-  <si>
-    <t>30001,180066,20065,20066,21006</t>
+    <t>2066,4007,5011,3004</t>
+  </si>
+  <si>
+    <t>30001,180066,20065,20066,21008</t>
   </si>
   <si>
     <t>地狱烈焰</t>
@@ -267,10 +267,10 @@
     <t>（Lv56-60）—— 失落神域，法则化身</t>
   </si>
   <si>
-    <t>2012,4007,5012,3004</t>
-  </si>
-  <si>
-    <t>30001,180072,20071,20072,21006</t>
+    <t>2072,4007,5012,3004</t>
+  </si>
+  <si>
+    <t>30001,180072,20071,20072,21008</t>
   </si>
   <si>
     <t>装备，技能，珍宝，神兵符</t>
@@ -455,12 +455,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>

--- a/Excel/MapGroupConfig.xlsx
+++ b/Excel/MapGroupConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="12080"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="UnitProto" sheetId="1" r:id="rId1"/>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="72">
   <si>
     <t>_Id</t>
   </si>
@@ -207,7 +207,10 @@
     <t>2042,4007,5007,3004</t>
   </si>
   <si>
-    <t>30001,180042,20041,20042,21007</t>
+    <t>30001,180042,20041,20042,21007,21</t>
+  </si>
+  <si>
+    <t>1,1,2,2,10,10,30</t>
   </si>
   <si>
     <t>冰封王陵</t>
@@ -219,7 +222,7 @@
     <t>2048,4007,5008,3004</t>
   </si>
   <si>
-    <t>30001,180048,20047,20048,21008</t>
+    <t>30001,180048,20047,20048,21008,22</t>
   </si>
   <si>
     <t>暗影祭坛</t>
@@ -231,7 +234,7 @@
     <t>2054,4007,5009,3004</t>
   </si>
   <si>
-    <t>30001,180054,20053,20054,21008</t>
+    <t>30001,180054,20053,20054,21008,23</t>
   </si>
   <si>
     <t>蛮族之地</t>
@@ -243,7 +246,7 @@
     <t>2060,4007,5010,3004</t>
   </si>
   <si>
-    <t>30001,180060,20059,20060,21008</t>
+    <t>30001,180060,20059,20060,21008,24</t>
   </si>
   <si>
     <t>#</t>
@@ -258,7 +261,7 @@
     <t>2066,4007,5011,3004</t>
   </si>
   <si>
-    <t>30001,180066,20065,20066,21008</t>
+    <t>30001,180066,20065,20066,21008,25</t>
   </si>
   <si>
     <t>地狱烈焰</t>
@@ -270,13 +273,13 @@
     <t>2072,4007,5012,3004</t>
   </si>
   <si>
-    <t>30001,180072,20071,20072,21008</t>
+    <t>30001,180072,20071,20072,21008,26</t>
   </si>
   <si>
     <t>装备，技能，珍宝，神兵符</t>
   </si>
   <si>
-    <t>四格，宠物，衣服，武器，传奇装备</t>
+    <t>四格，宠物，衣服，武器，传奇装备,魂环</t>
   </si>
 </sst>
 </file>
@@ -1293,7 +1296,7 @@
     <col min="6" max="6" width="40.4545454545455" style="1" customWidth="1"/>
     <col min="7" max="7" width="24.2727272727273" style="1" customWidth="1"/>
     <col min="8" max="8" width="21.0909090909091" style="1" customWidth="1"/>
-    <col min="9" max="9" width="33.6363636363636" style="1" customWidth="1"/>
+    <col min="9" max="9" width="37.8181818181818" style="1" customWidth="1"/>
     <col min="10" max="10" width="24.2727272727273" style="1" customWidth="1"/>
     <col min="11" max="11" width="12.9090909090909" style="1" customWidth="1"/>
     <col min="12" max="12" width="12" style="1" customWidth="1"/>
@@ -1590,7 +1593,7 @@
         <v>47</v>
       </c>
       <c r="J12" s="4" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="K12" s="3"/>
       <c r="L12" s="3"/>
@@ -1601,25 +1604,25 @@
         <v>8</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E13" s="1">
         <v>1</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H13" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J13" s="4" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="K13" s="3"/>
       <c r="L13" s="3"/>
@@ -1630,25 +1633,25 @@
         <v>9</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E14" s="1">
         <v>1</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H14" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="J14" s="4" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="K14" s="3"/>
       <c r="L14" s="3"/>
@@ -1659,25 +1662,25 @@
         <v>10</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E15" s="1">
         <v>1</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H15" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="J15" s="4" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="K15" s="3"/>
       <c r="L15" s="3"/>
@@ -1685,34 +1688,34 @@
     </row>
     <row r="16" customHeight="1" spans="1:14">
       <c r="A16" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C16" s="1">
         <v>11</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E16" s="1">
         <v>1</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H16" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I16" s="5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="J16" s="4" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
@@ -1720,34 +1723,34 @@
     </row>
     <row r="17" customHeight="1" spans="1:14">
       <c r="A17" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C17" s="1">
         <v>12</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E17" s="1">
         <v>1</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H17" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I17" s="5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="J17" s="4" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="K17" s="3"/>
       <c r="L17" s="3"/>
@@ -1755,18 +1758,18 @@
     </row>
     <row r="29" customHeight="1" spans="1:14">
       <c r="G29" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="30" customHeight="1" spans="1:14">
       <c r="A30" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/MapGroupConfig.xlsx
+++ b/Excel/MapGroupConfig.xlsx
@@ -150,7 +150,7 @@
     <t>30001,180018,20017,20018,21003</t>
   </si>
   <si>
-    <t>1,1,2,2,7,10</t>
+    <t>1,1,2,2,7</t>
   </si>
   <si>
     <t>迷雾森林</t>
@@ -162,10 +162,10 @@
     <t>2024,4007,5004,3004</t>
   </si>
   <si>
-    <t>30001,180024,20023,20024,21004</t>
-  </si>
-  <si>
-    <t>1,1,2,2,8,10</t>
+    <t>30001,180024,20023,20024,21004,21</t>
+  </si>
+  <si>
+    <t>1,1,2,2,8</t>
   </si>
   <si>
     <t>亡者荒漠</t>
@@ -177,10 +177,10 @@
     <t>2030,4007,5005,3004</t>
   </si>
   <si>
-    <t>30001,180030,20029,20030,21005</t>
-  </si>
-  <si>
-    <t>1,1,2,2,9,10</t>
+    <t>30001,180030,20029,20030,21005,21</t>
+  </si>
+  <si>
+    <t>1,1,2,2,9</t>
   </si>
   <si>
     <t>蛮鬃林地</t>
@@ -192,10 +192,10 @@
     <t>2036,4007,5006,3004</t>
   </si>
   <si>
-    <t>30001,180036,20035,20036,21006</t>
-  </si>
-  <si>
-    <t>1,1,2,2,10,10</t>
+    <t>30001,180036,20035,20036,21006,22</t>
+  </si>
+  <si>
+    <t>1,1,2,2,10</t>
   </si>
   <si>
     <t>熔岩地穴</t>
@@ -207,10 +207,10 @@
     <t>2042,4007,5007,3004</t>
   </si>
   <si>
-    <t>30001,180042,20041,20042,21007,21</t>
-  </si>
-  <si>
-    <t>1,1,2,2,10,10,30</t>
+    <t>30001,180042,20041,20042,21007,22</t>
+  </si>
+  <si>
+    <t>1,1,2,2,10,20</t>
   </si>
   <si>
     <t>冰封王陵</t>
@@ -222,7 +222,7 @@
     <t>2048,4007,5008,3004</t>
   </si>
   <si>
-    <t>30001,180048,20047,20048,21008,22</t>
+    <t>30001,180048,20047,20048,21008,23</t>
   </si>
   <si>
     <t>暗影祭坛</t>
@@ -234,7 +234,7 @@
     <t>2054,4007,5009,3004</t>
   </si>
   <si>
-    <t>30001,180054,20053,20054,21008,23</t>
+    <t>30001,180054,20053,20054,21009,23</t>
   </si>
   <si>
     <t>蛮族之地</t>
@@ -246,7 +246,7 @@
     <t>2060,4007,5010,3004</t>
   </si>
   <si>
-    <t>30001,180060,20059,20060,21008,24</t>
+    <t>30001,180060,20059,20060,21010,24</t>
   </si>
   <si>
     <t>#</t>
@@ -261,7 +261,7 @@
     <t>2066,4007,5011,3004</t>
   </si>
   <si>
-    <t>30001,180066,20065,20066,21008,25</t>
+    <t>30001,180066,20065,20066,21011,25</t>
   </si>
   <si>
     <t>地狱烈焰</t>
@@ -273,7 +273,7 @@
     <t>2072,4007,5012,3004</t>
   </si>
   <si>
-    <t>30001,180072,20071,20072,21008,26</t>
+    <t>30001,180072,20071,20072,21012,26</t>
   </si>
   <si>
     <t>装备，技能，珍宝，神兵符</t>
@@ -458,12 +458,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>

--- a/Excel/MapGroupConfig.xlsx
+++ b/Excel/MapGroupConfig.xlsx
@@ -210,7 +210,7 @@
     <t>30001,180042,20041,20042,21007,22</t>
   </si>
   <si>
-    <t>1,1,2,2,10,20</t>
+    <t>1,1,2,2,10,10</t>
   </si>
   <si>
     <t>冰封王陵</t>

--- a/Excel/MapGroupConfig.xlsx
+++ b/Excel/MapGroupConfig.xlsx
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="71">
   <si>
     <t>_Id</t>
   </si>
@@ -165,7 +165,7 @@
     <t>30001,180024,20023,20024,21004,21</t>
   </si>
   <si>
-    <t>1,1,2,2,8</t>
+    <t>1,1,2,2,8,5</t>
   </si>
   <si>
     <t>亡者荒漠</t>
@@ -180,7 +180,7 @@
     <t>30001,180030,20029,20030,21005,21</t>
   </si>
   <si>
-    <t>1,1,2,2,9</t>
+    <t>1,1,2,2,9,5</t>
   </si>
   <si>
     <t>蛮鬃林地</t>
@@ -195,7 +195,7 @@
     <t>30001,180036,20035,20036,21006,22</t>
   </si>
   <si>
-    <t>1,1,2,2,10</t>
+    <t>1,1,2,2,10,5</t>
   </si>
   <si>
     <t>熔岩地穴</t>
@@ -208,9 +208,6 @@
   </si>
   <si>
     <t>30001,180042,20041,20042,21007,22</t>
-  </si>
-  <si>
-    <t>1,1,2,2,10,10</t>
   </si>
   <si>
     <t>冰封王陵</t>
@@ -458,12 +455,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1593,7 +1590,7 @@
         <v>47</v>
       </c>
       <c r="J12" s="4" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="K12" s="3"/>
       <c r="L12" s="3"/>
@@ -1604,25 +1601,25 @@
         <v>8</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E13" s="1">
         <v>1</v>
       </c>
       <c r="F13" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="G13" s="4" t="s">
         <v>50</v>
-      </c>
-      <c r="G13" s="4" t="s">
-        <v>51</v>
       </c>
       <c r="H13" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="J13" s="4" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="K13" s="3"/>
       <c r="L13" s="3"/>
@@ -1633,25 +1630,25 @@
         <v>9</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E14" s="1">
         <v>1</v>
       </c>
       <c r="F14" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="G14" s="4" t="s">
         <v>54</v>
-      </c>
-      <c r="G14" s="4" t="s">
-        <v>55</v>
       </c>
       <c r="H14" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="J14" s="4" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="K14" s="3"/>
       <c r="L14" s="3"/>
@@ -1662,25 +1659,25 @@
         <v>10</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E15" s="1">
         <v>1</v>
       </c>
       <c r="F15" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="G15" s="4" t="s">
         <v>58</v>
-      </c>
-      <c r="G15" s="4" t="s">
-        <v>59</v>
       </c>
       <c r="H15" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="J15" s="4" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="K15" s="3"/>
       <c r="L15" s="3"/>
@@ -1688,34 +1685,34 @@
     </row>
     <row r="16" customHeight="1" spans="1:14">
       <c r="A16" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C16" s="1">
         <v>11</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E16" s="1">
         <v>1</v>
       </c>
       <c r="F16" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="G16" s="4" t="s">
         <v>63</v>
-      </c>
-      <c r="G16" s="4" t="s">
-        <v>64</v>
       </c>
       <c r="H16" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I16" s="5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J16" s="4" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
@@ -1723,34 +1720,34 @@
     </row>
     <row r="17" customHeight="1" spans="1:14">
       <c r="A17" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C17" s="1">
         <v>12</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E17" s="1">
         <v>1</v>
       </c>
       <c r="F17" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="G17" s="4" t="s">
         <v>67</v>
-      </c>
-      <c r="G17" s="4" t="s">
-        <v>68</v>
       </c>
       <c r="H17" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I17" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="J17" s="4" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="K17" s="3"/>
       <c r="L17" s="3"/>
@@ -1758,18 +1755,18 @@
     </row>
     <row r="29" customHeight="1" spans="1:14">
       <c r="G29" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="I29" s="1" t="s">
         <v>70</v>
-      </c>
-      <c r="I29" s="1" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="30" customHeight="1" spans="1:14">
       <c r="A30" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/MapGroupConfig.xlsx
+++ b/Excel/MapGroupConfig.xlsx
@@ -165,7 +165,7 @@
     <t>30001,180024,20023,20024,21004,21</t>
   </si>
   <si>
-    <t>1,1,2,2,8,5</t>
+    <t>1,1,2,2,8,6</t>
   </si>
   <si>
     <t>亡者荒漠</t>
@@ -180,7 +180,7 @@
     <t>30001,180030,20029,20030,21005,21</t>
   </si>
   <si>
-    <t>1,1,2,2,9,5</t>
+    <t>1,1,2,2,9,6</t>
   </si>
   <si>
     <t>蛮鬃林地</t>
@@ -195,7 +195,7 @@
     <t>30001,180036,20035,20036,21006,22</t>
   </si>
   <si>
-    <t>1,1,2,2,10,5</t>
+    <t>1,1,2,2,10,6</t>
   </si>
   <si>
     <t>熔岩地穴</t>
@@ -455,12 +455,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>

--- a/Excel/MapGroupConfig.xlsx
+++ b/Excel/MapGroupConfig.xlsx
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="71">
   <si>
     <t>_Id</t>
   </si>
@@ -246,37 +246,37 @@
     <t>30001,180060,20059,20060,21010,24</t>
   </si>
   <si>
+    <t>虚空裂谷</t>
+  </si>
+  <si>
+    <t>（Lv51-55）—— 远古龙巢，龙族与亚龙</t>
+  </si>
+  <si>
+    <t>2066,4007,5011,3004</t>
+  </si>
+  <si>
+    <t>30001,180066,20065,20066,21011,25</t>
+  </si>
+  <si>
+    <t>地狱烈焰</t>
+  </si>
+  <si>
+    <t>（Lv56-60）—— 失落神域，法则化身</t>
+  </si>
+  <si>
+    <t>2072,4007,5012,3004</t>
+  </si>
+  <si>
+    <t>30001,180072,20071,20072,21012,26</t>
+  </si>
+  <si>
+    <t>装备，技能，珍宝，神兵符</t>
+  </si>
+  <si>
+    <t>四格，宠物，衣服，武器，传奇装备,魂环</t>
+  </si>
+  <si>
     <t>#</t>
-  </si>
-  <si>
-    <t>虚空裂谷</t>
-  </si>
-  <si>
-    <t>（Lv51-55）—— 远古龙巢，龙族与亚龙</t>
-  </si>
-  <si>
-    <t>2066,4007,5011,3004</t>
-  </si>
-  <si>
-    <t>30001,180066,20065,20066,21011,25</t>
-  </si>
-  <si>
-    <t>地狱烈焰</t>
-  </si>
-  <si>
-    <t>（Lv56-60）—— 失落神域，法则化身</t>
-  </si>
-  <si>
-    <t>2072,4007,5012,3004</t>
-  </si>
-  <si>
-    <t>30001,180072,20071,20072,21012,26</t>
-  </si>
-  <si>
-    <t>装备，技能，珍宝，神兵符</t>
-  </si>
-  <si>
-    <t>四格，宠物，衣服，武器，传奇装备,魂环</t>
   </si>
 </sst>
 </file>
@@ -1303,7 +1303,7 @@
     <col min="16378" max="16384" width="9.27272727272727" style="1"/>
   </cols>
   <sheetData>
-    <row r="3" customHeight="1" spans="1:14">
+    <row r="3" customHeight="1" spans="3:14">
       <c r="C3" s="2" t="s">
         <v>0</v>
       </c>
@@ -1333,7 +1333,7 @@
       <c r="M3" s="2"/>
       <c r="N3" s="2"/>
     </row>
-    <row r="4" customHeight="1" spans="1:14">
+    <row r="4" customHeight="1" spans="3:14">
       <c r="C4" s="2" t="s">
         <v>8</v>
       </c>
@@ -1363,7 +1363,7 @@
       <c r="M4" s="2"/>
       <c r="N4" s="2"/>
     </row>
-    <row r="5" customHeight="1" spans="1:14">
+    <row r="5" customHeight="1" spans="3:14">
       <c r="C5" s="2" t="s">
         <v>10</v>
       </c>
@@ -1393,7 +1393,7 @@
       <c r="M5" s="2"/>
       <c r="N5" s="2"/>
     </row>
-    <row r="6" customHeight="1" spans="1:14">
+    <row r="6" customHeight="1" spans="3:14">
       <c r="C6" s="1">
         <v>1</v>
       </c>
@@ -1422,7 +1422,7 @@
       <c r="L6" s="3"/>
       <c r="N6" s="3"/>
     </row>
-    <row r="7" customHeight="1" spans="1:14">
+    <row r="7" customHeight="1" spans="3:14">
       <c r="C7" s="1">
         <v>2</v>
       </c>
@@ -1451,7 +1451,7 @@
       <c r="L7" s="3"/>
       <c r="N7" s="3"/>
     </row>
-    <row r="8" customHeight="1" spans="1:14">
+    <row r="8" customHeight="1" spans="3:14">
       <c r="C8" s="1">
         <v>3</v>
       </c>
@@ -1480,7 +1480,7 @@
       <c r="L8" s="3"/>
       <c r="N8" s="3"/>
     </row>
-    <row r="9" customHeight="1" spans="1:14">
+    <row r="9" customHeight="1" spans="3:14">
       <c r="C9" s="1">
         <v>4</v>
       </c>
@@ -1509,7 +1509,7 @@
       <c r="L9" s="3"/>
       <c r="N9" s="3"/>
     </row>
-    <row r="10" customHeight="1" spans="1:14">
+    <row r="10" customHeight="1" spans="3:14">
       <c r="C10" s="1">
         <v>5</v>
       </c>
@@ -1538,7 +1538,7 @@
       <c r="L10" s="3"/>
       <c r="N10" s="3"/>
     </row>
-    <row r="11" customHeight="1" spans="1:14">
+    <row r="11" customHeight="1" spans="3:14">
       <c r="C11" s="1">
         <v>6</v>
       </c>
@@ -1567,7 +1567,7 @@
       <c r="L11" s="3"/>
       <c r="N11" s="3"/>
     </row>
-    <row r="12" customHeight="1" spans="1:14">
+    <row r="12" customHeight="1" spans="3:14">
       <c r="C12" s="1">
         <v>7</v>
       </c>
@@ -1596,7 +1596,7 @@
       <c r="L12" s="3"/>
       <c r="N12" s="3"/>
     </row>
-    <row r="13" customHeight="1" spans="1:14">
+    <row r="13" customHeight="1" spans="3:14">
       <c r="C13" s="1">
         <v>8</v>
       </c>
@@ -1625,7 +1625,7 @@
       <c r="L13" s="3"/>
       <c r="N13" s="3"/>
     </row>
-    <row r="14" customHeight="1" spans="1:14">
+    <row r="14" customHeight="1" spans="3:14">
       <c r="C14" s="1">
         <v>9</v>
       </c>
@@ -1654,7 +1654,7 @@
       <c r="L14" s="3"/>
       <c r="N14" s="3"/>
     </row>
-    <row r="15" customHeight="1" spans="1:14">
+    <row r="15" customHeight="1" spans="3:14">
       <c r="C15" s="1">
         <v>10</v>
       </c>
@@ -1683,33 +1683,27 @@
       <c r="L15" s="3"/>
       <c r="N15" s="3"/>
     </row>
-    <row r="16" customHeight="1" spans="1:14">
-      <c r="A16" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>60</v>
-      </c>
+    <row r="16" customHeight="1" spans="3:14">
       <c r="C16" s="1">
         <v>11</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E16" s="1">
         <v>1</v>
       </c>
       <c r="F16" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="G16" s="4" t="s">
         <v>62</v>
-      </c>
-      <c r="G16" s="4" t="s">
-        <v>63</v>
       </c>
       <c r="H16" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I16" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J16" s="4" t="s">
         <v>43</v>
@@ -1719,32 +1713,26 @@
       <c r="N16" s="3"/>
     </row>
     <row r="17" customHeight="1" spans="1:14">
-      <c r="A17" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>60</v>
-      </c>
       <c r="C17" s="1">
         <v>12</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E17" s="1">
         <v>1</v>
       </c>
       <c r="F17" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="G17" s="4" t="s">
         <v>66</v>
-      </c>
-      <c r="G17" s="4" t="s">
-        <v>67</v>
       </c>
       <c r="H17" s="4" t="s">
         <v>16</v>
       </c>
       <c r="I17" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="J17" s="4" t="s">
         <v>43</v>
@@ -1755,18 +1743,18 @@
     </row>
     <row r="29" customHeight="1" spans="1:14">
       <c r="G29" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="I29" s="1" t="s">
         <v>69</v>
-      </c>
-      <c r="I29" s="1" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="30" customHeight="1" spans="1:14">
       <c r="A30" s="1" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
     </row>
   </sheetData>
